--- a/Result/profitability/6153.xlsx
+++ b/Result/profitability/6153.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0275</v>
+        <v>-0.8125</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.23625</v>
+        <v>-12.5275</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.78</v>
+        <v>-0.7162499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.29375</v>
+        <v>-8.59625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.64375</v>
+        <v>-0.55375</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.253749999999999</v>
+        <v>-2.6575</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4837500000000001</v>
+        <v>-0.3875</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8924999999999996</v>
+        <v>1.1175</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.34625</v>
+        <v>-0.29125</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8375</v>
+        <v>4.96625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.245</v>
+        <v>-0.0925</v>
       </c>
       <c r="N7" t="n">
-        <v>7.395</v>
+        <v>9.67375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0275</v>
+        <v>0.05875000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>12.25875</v>
+        <v>13.10125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1551</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1581</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-299</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-19.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>106</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-193</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-194</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.01375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-15.2225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4464285714285715</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.739999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.7747126436781608</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.712962962962963</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.8913525498891353</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
